--- a/random_CDS_jbst_extended.xlsx
+++ b/random_CDS_jbst_extended.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\merag\Git\JBioSeqTools_benchmark\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0D45004-1768-4F56-A133-50D0E472105E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCA99388-4C27-4559-AE77-CA38CBB133C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="238">
   <si>
     <t>id</t>
   </si>
@@ -731,6 +731,9 @@
   </si>
   <si>
     <t>ATGAAGCTGAACATGGCCGAGGAAGAAGATTATATGTCCGATTCTTTTATCAATGTGCAGGAGGACATCCGGCCTGGACTGCCAATGCTGAGACAGATCAGGGAGGCCCGGAGGAAGGAAGAGAAGCAGCAGGAGGCCAACCTGAAGAACAGACAGAAAAGCCTGAAGGAGGAAGAACAGGAGAGGAGAGACATCGGACTGAAGAACGCCCTCGGCTGTGAGAATAAAGGCTTCGCCCTGCTGCAGAAGATGGGTTACAAGTCCGGCCAGGCCCTGGGCAAGTCCGGGGGCGGCATTGTGGAGCCCATTCCTCTTAATATCAAGACAGGGAAGTCCGGCATCGGCCACGAGGCCAGCCTGAAAAGAAAAGCCGAGGAGAAGCTGGAGAGTTACCGCAAGAAGATTCACATGAAGAATCAGGCCGAGGAGAAGGCCGCTGAGCAGTTCAGAATGAGACTCAAGAACAAGCAGGACGAGATGAAACTGGAGGGGGACCTGCGGAGAAGCCAGCGGGCCTGTCAGCAGCTGGACGTGCAGAAGAACATCCAGGTGCCTAGAGAGGCCTGGTACTGGCTGCGCCTGGAGGAGGAGACTGAGGAGGATGAGGAGGAGAAGGAACAGGACGAGGACGAATACAAGTCTGAGGACCTGAGCGTGCTGGAGAAACTCCAGATCCTGACTTCCTACCTGAGAGAGGAGCACCTGTACTGTATCTGGTGCGGCACAGCCTATGAGGATAAAGAAGACCTGTCCAGCAATTGCCCCGGCCCTACCAGCGCCGATCACGATTGA</t>
+  </si>
+  <si>
+    <t>genscript_sequence</t>
   </si>
 </sst>
 </file>
@@ -773,7 +776,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -783,18 +786,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -826,7 +817,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -837,15 +828,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
@@ -1148,19 +1134,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U31"/>
+  <dimension ref="A1:V31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="5" width="8.88671875" style="3"/>
-    <col min="6" max="6" width="8.88671875" style="7"/>
-    <col min="7" max="18" width="8.88671875" style="3"/>
+    <col min="1" max="18" width="8.88671875" style="3"/>
     <col min="19" max="19" width="13.21875" style="5" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.88671875" style="3"/>
-    <col min="21" max="21" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="8.88671875" style="3"/>
+    <col min="20" max="20" width="20.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="8.88671875" style="3"/>
+    <col min="23" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1176,7 +1160,7 @@
       <c r="E1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -1218,1831 +1202,1834 @@
       <c r="S1" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="U1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="U1" s="3" t="s">
-        <v>206</v>
+      <c r="V1" t="s">
+        <v>237</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2" s="3">
         <v>2448</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2" s="3">
         <v>59.068627450980387</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I2" s="8">
+      <c r="I2" s="3">
         <v>0.41</v>
       </c>
-      <c r="J2" s="8">
+      <c r="J2" s="3">
         <v>-948.79998779296875</v>
       </c>
-      <c r="K2" s="8">
+      <c r="K2" s="3">
         <v>58.864379084967332</v>
       </c>
-      <c r="L2" s="8">
+      <c r="L2" s="3">
         <v>0.44</v>
       </c>
-      <c r="M2" s="8">
-        <v>4</v>
-      </c>
-      <c r="N2" s="8">
+      <c r="M2" s="3">
+        <v>4</v>
+      </c>
+      <c r="N2" s="3">
         <v>3</v>
       </c>
-      <c r="O2" s="8">
+      <c r="O2" s="3">
         <v>5</v>
       </c>
-      <c r="P2" s="8">
+      <c r="P2" s="3">
         <v>6</v>
       </c>
-      <c r="Q2" s="8">
+      <c r="Q2" s="3">
         <v>42</v>
       </c>
-      <c r="R2" s="8">
+      <c r="R2" s="3">
         <v>17</v>
       </c>
-      <c r="S2" s="9" t="s">
+      <c r="S2" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="T2" s="8">
+      <c r="T2" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="U2" s="3">
         <v>-924.4000244140625</v>
       </c>
-      <c r="U2" s="8" t="s">
-        <v>207</v>
-      </c>
     </row>
-    <row r="3" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="3">
         <v>2886</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="3">
         <v>64.137214137214144</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="I3" s="8">
+      <c r="I3" s="3">
         <v>0.39</v>
       </c>
-      <c r="J3" s="8">
+      <c r="J3" s="3">
         <v>-1158.099975585938</v>
       </c>
-      <c r="K3" s="8">
+      <c r="K3" s="3">
         <v>58.385308385308377</v>
       </c>
-      <c r="L3" s="8">
+      <c r="L3" s="3">
         <v>0.4</v>
       </c>
-      <c r="M3" s="8">
-        <v>4</v>
-      </c>
-      <c r="N3" s="8">
+      <c r="M3" s="3">
+        <v>4</v>
+      </c>
+      <c r="N3" s="3">
         <v>5</v>
       </c>
-      <c r="O3" s="8">
+      <c r="O3" s="3">
         <v>5</v>
       </c>
-      <c r="P3" s="8">
-        <v>4</v>
-      </c>
-      <c r="Q3" s="8">
+      <c r="P3" s="3">
+        <v>4</v>
+      </c>
+      <c r="Q3" s="3">
         <v>56</v>
       </c>
-      <c r="R3" s="8">
+      <c r="R3" s="3">
         <v>22</v>
       </c>
-      <c r="S3" s="9" t="s">
+      <c r="S3" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="T3" s="8">
+      <c r="T3" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="U3" s="3">
         <v>-1299.400024414062</v>
       </c>
-      <c r="U3" s="8" t="s">
-        <v>208</v>
-      </c>
     </row>
-    <row r="4" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="3">
         <v>3816</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="3">
         <v>68.763102725366878</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I4" s="8">
+      <c r="I4" s="3">
         <v>0.39</v>
       </c>
-      <c r="J4" s="8">
+      <c r="J4" s="3">
         <v>-1562.5</v>
       </c>
-      <c r="K4" s="8">
+      <c r="K4" s="3">
         <v>58.307127882599588</v>
       </c>
-      <c r="L4" s="8">
+      <c r="L4" s="3">
         <v>0.38</v>
       </c>
-      <c r="M4" s="8">
-        <v>4</v>
-      </c>
-      <c r="N4" s="8">
+      <c r="M4" s="3">
+        <v>4</v>
+      </c>
+      <c r="N4" s="3">
         <v>5</v>
       </c>
-      <c r="O4" s="8">
+      <c r="O4" s="3">
         <v>5</v>
       </c>
-      <c r="P4" s="8">
+      <c r="P4" s="3">
         <v>5</v>
       </c>
-      <c r="Q4" s="8">
+      <c r="Q4" s="3">
         <v>57</v>
       </c>
-      <c r="R4" s="8">
+      <c r="R4" s="3">
         <v>23</v>
       </c>
-      <c r="S4" s="9" t="s">
+      <c r="S4" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="T4" s="8">
+      <c r="T4" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="U4" s="3">
         <v>-1898.199951171875</v>
       </c>
-      <c r="U4" s="8" t="s">
-        <v>209</v>
-      </c>
     </row>
-    <row r="5" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="3">
         <v>3738</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="3">
         <v>58.881754949170677</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="I5" s="8">
+      <c r="I5" s="3">
         <v>0.42</v>
       </c>
-      <c r="J5" s="8">
+      <c r="J5" s="3">
         <v>-1414.160034179688</v>
       </c>
-      <c r="K5" s="8">
+      <c r="K5" s="3">
         <v>58.052434456928843</v>
       </c>
-      <c r="L5" s="8">
+      <c r="L5" s="3">
         <v>0.44</v>
       </c>
-      <c r="M5" s="8">
-        <v>4</v>
-      </c>
-      <c r="N5" s="8">
+      <c r="M5" s="3">
+        <v>4</v>
+      </c>
+      <c r="N5" s="3">
         <v>6</v>
       </c>
-      <c r="O5" s="8">
+      <c r="O5" s="3">
         <v>6</v>
       </c>
-      <c r="P5" s="8">
+      <c r="P5" s="3">
         <v>3</v>
       </c>
-      <c r="Q5" s="8">
+      <c r="Q5" s="3">
         <v>50</v>
       </c>
-      <c r="R5" s="8">
+      <c r="R5" s="3">
         <v>19</v>
       </c>
-      <c r="S5" s="9" t="s">
+      <c r="S5" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="T5" s="8">
+      <c r="T5" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="U5" s="3">
         <v>-1447.099975585938</v>
       </c>
-      <c r="U5" s="8" t="s">
-        <v>210</v>
-      </c>
     </row>
-    <row r="6" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="3">
         <v>2754</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="3">
         <v>59.622367465504723</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="3">
         <v>0.39</v>
       </c>
-      <c r="J6" s="8">
+      <c r="J6" s="3">
         <v>-1115.099975585938</v>
       </c>
-      <c r="K6" s="8">
+      <c r="K6" s="3">
         <v>58.859840232389253</v>
       </c>
-      <c r="L6" s="8">
+      <c r="L6" s="3">
         <v>0.41</v>
       </c>
-      <c r="M6" s="8">
-        <v>4</v>
-      </c>
-      <c r="N6" s="8">
+      <c r="M6" s="3">
+        <v>4</v>
+      </c>
+      <c r="N6" s="3">
         <v>6</v>
       </c>
-      <c r="O6" s="8">
+      <c r="O6" s="3">
         <v>5</v>
       </c>
-      <c r="P6" s="8">
-        <v>4</v>
-      </c>
-      <c r="Q6" s="8">
+      <c r="P6" s="3">
+        <v>4</v>
+      </c>
+      <c r="Q6" s="3">
         <v>56</v>
       </c>
-      <c r="R6" s="8">
+      <c r="R6" s="3">
         <v>23</v>
       </c>
-      <c r="S6" s="9" t="s">
+      <c r="S6" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="T6" s="8">
+      <c r="T6" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="U6" s="3">
         <v>-1137.800048828125</v>
       </c>
-      <c r="U6" s="8" t="s">
-        <v>211</v>
-      </c>
     </row>
-    <row r="7" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="3">
         <v>3759</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="3">
         <v>38.22825219473264</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="H7" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="I7" s="8">
+      <c r="I7" s="3">
         <v>0.37</v>
       </c>
-      <c r="J7" s="8">
+      <c r="J7" s="3">
         <v>-1408.199951171875</v>
       </c>
-      <c r="K7" s="8">
+      <c r="K7" s="3">
         <v>59.271082734769877</v>
       </c>
-      <c r="L7" s="8">
+      <c r="L7" s="3">
         <v>0.48</v>
       </c>
-      <c r="M7" s="8">
-        <v>4</v>
-      </c>
-      <c r="N7" s="8">
+      <c r="M7" s="3">
+        <v>4</v>
+      </c>
+      <c r="N7" s="3">
         <v>6</v>
       </c>
-      <c r="O7" s="8">
+      <c r="O7" s="3">
         <v>6</v>
       </c>
-      <c r="P7" s="8">
+      <c r="P7" s="3">
         <v>5</v>
       </c>
-      <c r="Q7" s="8">
+      <c r="Q7" s="3">
         <v>68</v>
       </c>
-      <c r="R7" s="8">
+      <c r="R7" s="3">
         <v>27</v>
       </c>
-      <c r="S7" s="9" t="s">
+      <c r="S7" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="T7" s="8">
+      <c r="T7" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="U7" s="3">
         <v>-917.20001220703125</v>
       </c>
-      <c r="U7" s="8" t="s">
-        <v>212</v>
-      </c>
     </row>
-    <row r="8" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="3">
         <v>2172</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="3">
         <v>41.804788213627987</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="I8" s="8">
+      <c r="I8" s="3">
         <v>0.34</v>
       </c>
-      <c r="J8" s="8">
+      <c r="J8" s="3">
         <v>-819</v>
       </c>
-      <c r="K8" s="8">
+      <c r="K8" s="3">
         <v>58.885819521178639</v>
       </c>
-      <c r="L8" s="8">
+      <c r="L8" s="3">
         <v>0.44</v>
       </c>
-      <c r="M8" s="8">
-        <v>4</v>
-      </c>
-      <c r="N8" s="8">
+      <c r="M8" s="3">
+        <v>4</v>
+      </c>
+      <c r="N8" s="3">
         <v>6</v>
       </c>
-      <c r="O8" s="8">
-        <v>4</v>
-      </c>
-      <c r="P8" s="8">
+      <c r="O8" s="3">
+        <v>4</v>
+      </c>
+      <c r="P8" s="3">
         <v>3</v>
       </c>
-      <c r="Q8" s="8">
+      <c r="Q8" s="3">
         <v>68</v>
       </c>
-      <c r="R8" s="8">
+      <c r="R8" s="3">
         <v>26</v>
       </c>
-      <c r="S8" s="9" t="s">
+      <c r="S8" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="T8" s="8">
+      <c r="T8" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="U8" s="3">
         <v>-589.20001220703125</v>
       </c>
-      <c r="U8" s="8" t="s">
-        <v>213</v>
-      </c>
     </row>
-    <row r="9" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="3">
         <v>8034</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="3">
         <v>40.851381628080659</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="I9" s="8">
+      <c r="I9" s="3">
         <v>0.36</v>
       </c>
-      <c r="J9" s="8">
+      <c r="J9" s="3">
         <v>-2966.199951171875</v>
       </c>
-      <c r="K9" s="8">
+      <c r="K9" s="3">
         <v>59.210853871048037</v>
       </c>
-      <c r="L9" s="8">
+      <c r="L9" s="3">
         <v>0.46</v>
       </c>
-      <c r="M9" s="8">
-        <v>4</v>
-      </c>
-      <c r="N9" s="8">
+      <c r="M9" s="3">
+        <v>4</v>
+      </c>
+      <c r="N9" s="3">
         <v>5</v>
       </c>
-      <c r="O9" s="8">
+      <c r="O9" s="3">
         <v>6</v>
       </c>
-      <c r="P9" s="8">
-        <v>4</v>
-      </c>
-      <c r="Q9" s="8">
+      <c r="P9" s="3">
+        <v>4</v>
+      </c>
+      <c r="Q9" s="3">
         <v>69</v>
       </c>
-      <c r="R9" s="8">
+      <c r="R9" s="3">
         <v>28</v>
       </c>
-      <c r="S9" s="9" t="s">
+      <c r="S9" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="T9" s="8">
+      <c r="T9" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="U9" s="3">
         <v>-2131</v>
       </c>
-      <c r="U9" s="8" t="s">
-        <v>214</v>
-      </c>
     </row>
-    <row r="10" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="3">
         <v>2523</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="3">
         <v>41.65675782798256</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="G10" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="H10" s="8" t="s">
+      <c r="H10" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="I10" s="8">
+      <c r="I10" s="3">
         <v>0.35</v>
       </c>
-      <c r="J10" s="8">
+      <c r="J10" s="3">
         <v>-966.79998779296875</v>
       </c>
-      <c r="K10" s="8">
+      <c r="K10" s="3">
         <v>58.382877526753859</v>
       </c>
-      <c r="L10" s="8">
+      <c r="L10" s="3">
         <v>0.44</v>
       </c>
-      <c r="M10" s="8">
-        <v>4</v>
-      </c>
-      <c r="N10" s="8">
+      <c r="M10" s="3">
+        <v>4</v>
+      </c>
+      <c r="N10" s="3">
         <v>6</v>
       </c>
-      <c r="O10" s="8">
+      <c r="O10" s="3">
         <v>6</v>
       </c>
-      <c r="P10" s="8">
+      <c r="P10" s="3">
         <v>3</v>
       </c>
-      <c r="Q10" s="8">
+      <c r="Q10" s="3">
         <v>69</v>
       </c>
-      <c r="R10" s="8">
+      <c r="R10" s="3">
         <v>27</v>
       </c>
-      <c r="S10" s="9" t="s">
+      <c r="S10" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="T10" s="8">
+      <c r="T10" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="U10" s="3">
         <v>-692</v>
       </c>
-      <c r="U10" s="8" t="s">
-        <v>215</v>
-      </c>
     </row>
-    <row r="11" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="3">
         <v>3666</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="3">
         <v>41.653027823240592</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G11" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="H11" s="8" t="s">
+      <c r="H11" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="I11" s="8">
+      <c r="I11" s="3">
         <v>0.37</v>
       </c>
-      <c r="J11" s="8">
+      <c r="J11" s="3">
         <v>-1390.199951171875</v>
       </c>
-      <c r="K11" s="8">
+      <c r="K11" s="3">
         <v>59.519912711402071</v>
       </c>
-      <c r="L11" s="8">
+      <c r="L11" s="3">
         <v>0.46</v>
       </c>
-      <c r="M11" s="8">
-        <v>4</v>
-      </c>
-      <c r="N11" s="8">
+      <c r="M11" s="3">
+        <v>4</v>
+      </c>
+      <c r="N11" s="3">
         <v>3</v>
       </c>
-      <c r="O11" s="8">
+      <c r="O11" s="3">
         <v>6</v>
       </c>
-      <c r="P11" s="8">
+      <c r="P11" s="3">
         <v>5</v>
       </c>
-      <c r="Q11" s="8">
+      <c r="Q11" s="3">
         <v>65</v>
       </c>
-      <c r="R11" s="8">
+      <c r="R11" s="3">
         <v>26</v>
       </c>
-      <c r="S11" s="9" t="s">
+      <c r="S11" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="T11" s="8">
+      <c r="T11" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="U11" s="3">
         <v>-972.0999755859375</v>
       </c>
-      <c r="U11" s="8" t="s">
-        <v>216</v>
-      </c>
     </row>
-    <row r="12" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="3">
         <v>867</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="3">
         <v>58.362168396770478</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="F12" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G12" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="H12" s="8" t="s">
+      <c r="H12" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="I12" s="8">
+      <c r="I12" s="3">
         <v>0.39</v>
       </c>
-      <c r="J12" s="8">
+      <c r="J12" s="3">
         <v>-339.5</v>
       </c>
-      <c r="K12" s="8">
+      <c r="K12" s="3">
         <v>58.82352941176471</v>
       </c>
-      <c r="L12" s="8">
+      <c r="L12" s="3">
         <v>0.42</v>
       </c>
-      <c r="M12" s="8">
-        <v>4</v>
-      </c>
-      <c r="N12" s="8">
-        <v>4</v>
-      </c>
-      <c r="O12" s="8">
-        <v>4</v>
-      </c>
-      <c r="P12" s="8">
-        <v>4</v>
-      </c>
-      <c r="Q12" s="8">
+      <c r="M12" s="3">
+        <v>4</v>
+      </c>
+      <c r="N12" s="3">
+        <v>4</v>
+      </c>
+      <c r="O12" s="3">
+        <v>4</v>
+      </c>
+      <c r="P12" s="3">
+        <v>4</v>
+      </c>
+      <c r="Q12" s="3">
         <v>52</v>
       </c>
-      <c r="R12" s="8">
+      <c r="R12" s="3">
         <v>21</v>
       </c>
-      <c r="S12" s="9" t="s">
+      <c r="S12" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="T12" s="8">
+      <c r="T12" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="U12" s="3">
         <v>-327.5</v>
       </c>
-      <c r="U12" s="8" t="s">
-        <v>217</v>
-      </c>
     </row>
-    <row r="13" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="3">
         <v>1410</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="3">
         <v>59.432624113475171</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="G13" s="8" t="s">
+      <c r="G13" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="H13" s="8" t="s">
+      <c r="H13" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="I13" s="8">
+      <c r="I13" s="3">
         <v>0.4</v>
       </c>
-      <c r="J13" s="8">
+      <c r="J13" s="3">
         <v>-540.79998779296875</v>
       </c>
-      <c r="K13" s="8">
+      <c r="K13" s="3">
         <v>58.439716312056731</v>
       </c>
-      <c r="L13" s="8">
+      <c r="L13" s="3">
         <v>0.42</v>
       </c>
-      <c r="M13" s="8">
-        <v>4</v>
-      </c>
-      <c r="N13" s="8">
+      <c r="M13" s="3">
+        <v>4</v>
+      </c>
+      <c r="N13" s="3">
         <v>5</v>
       </c>
-      <c r="O13" s="8">
+      <c r="O13" s="3">
         <v>5</v>
       </c>
-      <c r="P13" s="8">
+      <c r="P13" s="3">
         <v>5</v>
       </c>
-      <c r="Q13" s="8">
+      <c r="Q13" s="3">
         <v>51</v>
       </c>
-      <c r="R13" s="8">
+      <c r="R13" s="3">
         <v>20</v>
       </c>
-      <c r="S13" s="9" t="s">
+      <c r="S13" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="T13" s="8">
+      <c r="T13" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="U13" s="3">
         <v>-540.4000244140625</v>
       </c>
-      <c r="U13" s="8" t="s">
-        <v>218</v>
-      </c>
     </row>
-    <row r="14" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="3">
         <v>954</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="3">
         <v>64.779874213836479</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="G14" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="H14" s="8" t="s">
+      <c r="H14" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="I14" s="8">
+      <c r="I14" s="3">
         <v>0.4</v>
       </c>
-      <c r="J14" s="8">
+      <c r="J14" s="3">
         <v>-388.89999389648438</v>
       </c>
-      <c r="K14" s="8">
+      <c r="K14" s="3">
         <v>58.80503144654088</v>
       </c>
-      <c r="L14" s="8">
+      <c r="L14" s="3">
         <v>0.41</v>
       </c>
-      <c r="M14" s="8">
-        <v>4</v>
-      </c>
-      <c r="N14" s="8">
-        <v>4</v>
-      </c>
-      <c r="O14" s="8">
-        <v>4</v>
-      </c>
-      <c r="P14" s="8">
+      <c r="M14" s="3">
+        <v>4</v>
+      </c>
+      <c r="N14" s="3">
+        <v>4</v>
+      </c>
+      <c r="O14" s="3">
+        <v>4</v>
+      </c>
+      <c r="P14" s="3">
         <v>3</v>
       </c>
-      <c r="Q14" s="8">
+      <c r="Q14" s="3">
         <v>52</v>
       </c>
-      <c r="R14" s="8">
+      <c r="R14" s="3">
         <v>22</v>
       </c>
-      <c r="S14" s="9" t="s">
+      <c r="S14" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="T14" s="8">
+      <c r="T14" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="U14" s="3">
         <v>-445.60000610351563</v>
       </c>
-      <c r="U14" s="8" t="s">
-        <v>219</v>
-      </c>
     </row>
-    <row r="15" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="3">
         <v>1905</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="3">
         <v>60.787401574803148</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="F15" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="G15" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="H15" s="8" t="s">
+      <c r="H15" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="I15" s="8">
+      <c r="I15" s="3">
         <v>0.4</v>
       </c>
-      <c r="J15" s="8">
+      <c r="J15" s="3">
         <v>-777.79998779296875</v>
       </c>
-      <c r="K15" s="8">
+      <c r="K15" s="3">
         <v>58.582677165354333</v>
       </c>
-      <c r="L15" s="8">
+      <c r="L15" s="3">
         <v>0.42</v>
       </c>
-      <c r="M15" s="8">
-        <v>4</v>
-      </c>
-      <c r="N15" s="8">
-        <v>4</v>
-      </c>
-      <c r="O15" s="8">
-        <v>4</v>
-      </c>
-      <c r="P15" s="8">
+      <c r="M15" s="3">
+        <v>4</v>
+      </c>
+      <c r="N15" s="3">
+        <v>4</v>
+      </c>
+      <c r="O15" s="3">
+        <v>4</v>
+      </c>
+      <c r="P15" s="3">
         <v>3</v>
       </c>
-      <c r="Q15" s="8">
+      <c r="Q15" s="3">
         <v>51</v>
       </c>
-      <c r="R15" s="8">
+      <c r="R15" s="3">
         <v>20</v>
       </c>
-      <c r="S15" s="10" t="s">
+      <c r="S15" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="T15" s="8">
+      <c r="T15" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="U15" s="3">
         <v>-821.79998779296875</v>
       </c>
-      <c r="U15" s="8" t="s">
-        <v>220</v>
-      </c>
     </row>
-    <row r="16" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="3">
         <v>1095</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="3">
         <v>57.351598173515981</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="E16" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="F16" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="G16" s="8" t="s">
+      <c r="G16" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="H16" s="8" t="s">
+      <c r="H16" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="I16" s="8">
+      <c r="I16" s="3">
         <v>0.42</v>
       </c>
-      <c r="J16" s="8">
+      <c r="J16" s="3">
         <v>-427.29998779296881</v>
       </c>
-      <c r="K16" s="8">
+      <c r="K16" s="3">
         <v>57.80821917808219</v>
       </c>
-      <c r="L16" s="8">
+      <c r="L16" s="3">
         <v>0.45</v>
       </c>
-      <c r="M16" s="8">
-        <v>4</v>
-      </c>
-      <c r="N16" s="8">
+      <c r="M16" s="3">
+        <v>4</v>
+      </c>
+      <c r="N16" s="3">
         <v>3</v>
       </c>
-      <c r="O16" s="8">
+      <c r="O16" s="3">
         <v>6</v>
       </c>
-      <c r="P16" s="8">
+      <c r="P16" s="3">
         <v>6</v>
       </c>
-      <c r="Q16" s="8">
+      <c r="Q16" s="3">
         <v>47</v>
       </c>
-      <c r="R16" s="8">
+      <c r="R16" s="3">
         <v>19</v>
       </c>
-      <c r="S16" s="9" t="s">
+      <c r="S16" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="T16" s="8">
+      <c r="T16" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="U16" s="3">
         <v>-412.39999389648438</v>
       </c>
-      <c r="U16" s="8" t="s">
-        <v>221</v>
-      </c>
     </row>
-    <row r="17" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="3">
         <v>924</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="3">
         <v>41.125541125541133</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E17" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="F17" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="G17" s="8" t="s">
+      <c r="G17" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="H17" s="8" t="s">
+      <c r="H17" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="I17" s="8">
+      <c r="I17" s="3">
         <v>0.38</v>
       </c>
-      <c r="J17" s="8">
+      <c r="J17" s="3">
         <v>-337.29998779296881</v>
       </c>
-      <c r="K17" s="8">
+      <c r="K17" s="3">
         <v>59.199134199134193</v>
       </c>
-      <c r="L17" s="8">
+      <c r="L17" s="3">
         <v>0.47</v>
       </c>
-      <c r="M17" s="8">
-        <v>4</v>
-      </c>
-      <c r="N17" s="8">
+      <c r="M17" s="3">
+        <v>4</v>
+      </c>
+      <c r="N17" s="3">
         <v>3</v>
       </c>
-      <c r="O17" s="8">
+      <c r="O17" s="3">
         <v>6</v>
       </c>
-      <c r="P17" s="8">
+      <c r="P17" s="3">
         <v>3</v>
       </c>
-      <c r="Q17" s="8">
+      <c r="Q17" s="3">
         <v>62</v>
       </c>
-      <c r="R17" s="8">
+      <c r="R17" s="3">
         <v>25</v>
       </c>
-      <c r="S17" s="9" t="s">
+      <c r="S17" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="T17" s="8">
+      <c r="T17" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="U17" s="3">
         <v>-246.3999938964844</v>
       </c>
-      <c r="U17" s="8" t="s">
-        <v>222</v>
-      </c>
     </row>
-    <row r="18" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="3">
         <v>1527</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="3">
         <v>39.227242960052394</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="E18" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="F18" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="G18" s="8" t="s">
+      <c r="G18" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="H18" s="8" t="s">
+      <c r="H18" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="I18" s="8">
+      <c r="I18" s="3">
         <v>0.36</v>
       </c>
-      <c r="J18" s="8">
+      <c r="J18" s="3">
         <v>-567.0999755859375</v>
       </c>
-      <c r="K18" s="8">
+      <c r="K18" s="3">
         <v>59.790438768827769</v>
       </c>
-      <c r="L18" s="8">
+      <c r="L18" s="3">
         <v>0.47</v>
       </c>
-      <c r="M18" s="8">
+      <c r="M18" s="3">
         <v>3</v>
       </c>
-      <c r="N18" s="8">
+      <c r="N18" s="3">
         <v>3</v>
       </c>
-      <c r="O18" s="8">
+      <c r="O18" s="3">
         <v>5</v>
       </c>
-      <c r="P18" s="8">
+      <c r="P18" s="3">
         <v>3</v>
       </c>
-      <c r="Q18" s="8">
+      <c r="Q18" s="3">
         <v>73</v>
       </c>
-      <c r="R18" s="8">
+      <c r="R18" s="3">
         <v>29</v>
       </c>
-      <c r="S18" s="9" t="s">
+      <c r="S18" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="T18" s="8">
+      <c r="T18" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="U18" s="3">
         <v>-375.79998779296881</v>
       </c>
-      <c r="U18" s="8" t="s">
-        <v>223</v>
-      </c>
     </row>
-    <row r="19" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="s">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="3">
         <v>999</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="3">
         <v>40.840840840840841</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E19" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="F19" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="G19" s="8" t="s">
+      <c r="G19" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="H19" s="8" t="s">
+      <c r="H19" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="I19" s="8">
+      <c r="I19" s="3">
         <v>0.35</v>
       </c>
-      <c r="J19" s="8">
+      <c r="J19" s="3">
         <v>-355.70001220703119</v>
       </c>
-      <c r="K19" s="8">
+      <c r="K19" s="3">
         <v>57.957957957957959</v>
       </c>
-      <c r="L19" s="8">
+      <c r="L19" s="3">
         <v>0.45</v>
       </c>
-      <c r="M19" s="8">
+      <c r="M19" s="3">
         <v>3</v>
       </c>
-      <c r="N19" s="8">
-        <v>4</v>
-      </c>
-      <c r="O19" s="8">
-        <v>4</v>
-      </c>
-      <c r="P19" s="8">
+      <c r="N19" s="3">
+        <v>4</v>
+      </c>
+      <c r="O19" s="3">
+        <v>4</v>
+      </c>
+      <c r="P19" s="3">
         <v>3</v>
       </c>
-      <c r="Q19" s="8">
+      <c r="Q19" s="3">
         <v>73</v>
       </c>
-      <c r="R19" s="8">
+      <c r="R19" s="3">
         <v>29</v>
       </c>
-      <c r="S19" s="9" t="s">
+      <c r="S19" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="T19" s="8">
+      <c r="T19" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="U19" s="3">
         <v>-284.5</v>
       </c>
-      <c r="U19" s="8" t="s">
-        <v>224</v>
-      </c>
     </row>
-    <row r="20" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="8" t="s">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C20" s="8">
+      <c r="C20" s="3">
         <v>1416</v>
       </c>
-      <c r="D20" s="8">
+      <c r="D20" s="3">
         <v>38.135593220338983</v>
       </c>
-      <c r="E20" s="8" t="s">
+      <c r="E20" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="F20" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="G20" s="8" t="s">
+      <c r="G20" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="H20" s="8" t="s">
+      <c r="H20" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="I20" s="8">
+      <c r="I20" s="3">
         <v>0.35</v>
       </c>
-      <c r="J20" s="8">
+      <c r="J20" s="3">
         <v>-480.70001220703119</v>
       </c>
-      <c r="K20" s="8">
+      <c r="K20" s="3">
         <v>59.110169491525419</v>
       </c>
-      <c r="L20" s="8">
+      <c r="L20" s="3">
         <v>0.45</v>
       </c>
-      <c r="M20" s="8">
-        <v>4</v>
-      </c>
-      <c r="N20" s="8">
-        <v>4</v>
-      </c>
-      <c r="O20" s="8">
+      <c r="M20" s="3">
+        <v>4</v>
+      </c>
+      <c r="N20" s="3">
+        <v>4</v>
+      </c>
+      <c r="O20" s="3">
         <v>5</v>
       </c>
-      <c r="P20" s="8">
+      <c r="P20" s="3">
         <v>3</v>
       </c>
-      <c r="Q20" s="8">
+      <c r="Q20" s="3">
         <v>74</v>
       </c>
-      <c r="R20" s="8">
+      <c r="R20" s="3">
         <v>29</v>
       </c>
-      <c r="S20" s="9" t="s">
+      <c r="S20" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="T20" s="8">
+      <c r="T20" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="U20" s="3">
         <v>-350.20001220703119</v>
       </c>
-      <c r="U20" s="8" t="s">
-        <v>225</v>
-      </c>
     </row>
-    <row r="21" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="8" t="s">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C21" s="8">
+      <c r="C21" s="3">
         <v>909</v>
       </c>
-      <c r="D21" s="8">
+      <c r="D21" s="3">
         <v>39.163916391639162</v>
       </c>
-      <c r="E21" s="8" t="s">
+      <c r="E21" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="F21" s="8" t="s">
+      <c r="F21" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="G21" s="8" t="s">
+      <c r="G21" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="H21" s="8" t="s">
+      <c r="H21" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="I21" s="8">
+      <c r="I21" s="3">
         <v>0.38</v>
       </c>
-      <c r="J21" s="8">
+      <c r="J21" s="3">
         <v>-299.5</v>
       </c>
-      <c r="K21" s="8">
+      <c r="K21" s="3">
         <v>57.645764576457651</v>
       </c>
-      <c r="L21" s="8">
+      <c r="L21" s="3">
         <v>0.48</v>
       </c>
-      <c r="M21" s="8">
+      <c r="M21" s="3">
         <v>3</v>
       </c>
-      <c r="N21" s="8">
+      <c r="N21" s="3">
         <v>5</v>
       </c>
-      <c r="O21" s="8">
+      <c r="O21" s="3">
         <v>5</v>
       </c>
-      <c r="P21" s="8">
-        <v>4</v>
-      </c>
-      <c r="Q21" s="8">
+      <c r="P21" s="3">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="3">
         <v>67</v>
       </c>
-      <c r="R21" s="8">
+      <c r="R21" s="3">
         <v>25</v>
       </c>
-      <c r="S21" s="9" t="s">
+      <c r="S21" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="T21" s="8">
+      <c r="T21" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="U21" s="3">
         <v>-210.80000305175781</v>
       </c>
-      <c r="U21" s="8" t="s">
-        <v>226</v>
-      </c>
     </row>
-    <row r="22" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="8" t="s">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C22" s="8">
+      <c r="C22" s="3">
         <v>795</v>
       </c>
-      <c r="D22" s="8">
+      <c r="D22" s="3">
         <v>68.80503144654088</v>
       </c>
-      <c r="E22" s="8" t="s">
+      <c r="E22" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="F22" s="8" t="s">
+      <c r="F22" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="G22" s="8" t="s">
+      <c r="G22" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="H22" s="8" t="s">
+      <c r="H22" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="I22" s="8">
+      <c r="I22" s="3">
         <v>0.37</v>
       </c>
-      <c r="J22" s="8">
+      <c r="J22" s="3">
         <v>-312.70001220703119</v>
       </c>
-      <c r="K22" s="8">
+      <c r="K22" s="3">
         <v>58.616352201257861</v>
       </c>
-      <c r="L22" s="8">
+      <c r="L22" s="3">
         <v>0.38</v>
       </c>
-      <c r="M22" s="8">
-        <v>4</v>
-      </c>
-      <c r="N22" s="8">
-        <v>4</v>
-      </c>
-      <c r="O22" s="8">
-        <v>4</v>
-      </c>
-      <c r="P22" s="8">
+      <c r="M22" s="3">
+        <v>4</v>
+      </c>
+      <c r="N22" s="3">
+        <v>4</v>
+      </c>
+      <c r="O22" s="3">
+        <v>4</v>
+      </c>
+      <c r="P22" s="3">
         <v>3</v>
       </c>
-      <c r="Q22" s="8">
+      <c r="Q22" s="3">
         <v>58</v>
       </c>
-      <c r="R22" s="8">
+      <c r="R22" s="3">
         <v>24</v>
       </c>
-      <c r="S22" s="9" t="s">
+      <c r="S22" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="T22" s="8">
+      <c r="T22" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="U22" s="3">
         <v>-376.20001220703119</v>
       </c>
-      <c r="U22" s="8" t="s">
-        <v>227</v>
-      </c>
     </row>
-    <row r="23" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="8" t="s">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C23" s="8">
+      <c r="C23" s="3">
         <v>630</v>
       </c>
-      <c r="D23" s="8">
+      <c r="D23" s="3">
         <v>56.825396825396822</v>
       </c>
-      <c r="E23" s="8" t="s">
+      <c r="E23" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="F23" s="8" t="s">
+      <c r="F23" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="G23" s="8" t="s">
+      <c r="G23" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="H23" s="8" t="s">
+      <c r="H23" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="I23" s="8">
+      <c r="I23" s="3">
         <v>0.44</v>
       </c>
-      <c r="J23" s="8">
+      <c r="J23" s="3">
         <v>-217.8999938964844</v>
       </c>
-      <c r="K23" s="8">
+      <c r="K23" s="3">
         <v>56.507936507936513</v>
       </c>
-      <c r="L23" s="8">
+      <c r="L23" s="3">
         <v>0.47</v>
       </c>
-      <c r="M23" s="8">
-        <v>4</v>
-      </c>
-      <c r="N23" s="8">
-        <v>4</v>
-      </c>
-      <c r="O23" s="8">
-        <v>4</v>
-      </c>
-      <c r="P23" s="8">
+      <c r="M23" s="3">
+        <v>4</v>
+      </c>
+      <c r="N23" s="3">
+        <v>4</v>
+      </c>
+      <c r="O23" s="3">
+        <v>4</v>
+      </c>
+      <c r="P23" s="3">
         <v>6</v>
       </c>
-      <c r="Q23" s="8">
+      <c r="Q23" s="3">
         <v>44</v>
       </c>
-      <c r="R23" s="8">
+      <c r="R23" s="3">
         <v>16</v>
       </c>
-      <c r="S23" s="9" t="s">
+      <c r="S23" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="T23" s="8">
+      <c r="T23" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="U23" s="3">
         <v>-217.8999938964844</v>
       </c>
-      <c r="U23" s="8" t="s">
-        <v>228</v>
-      </c>
     </row>
-    <row r="24" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="8" t="s">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C24" s="8">
+      <c r="C24" s="3">
         <v>741</v>
       </c>
-      <c r="D24" s="8">
+      <c r="D24" s="3">
         <v>61.673414304993258</v>
       </c>
-      <c r="E24" s="8" t="s">
+      <c r="E24" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="F24" s="8" t="s">
+      <c r="F24" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="G24" s="8" t="s">
+      <c r="G24" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="H24" s="8" t="s">
+      <c r="H24" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="I24" s="8">
+      <c r="I24" s="3">
         <v>0.4</v>
       </c>
-      <c r="J24" s="8">
+      <c r="J24" s="3">
         <v>-297.60000610351563</v>
       </c>
-      <c r="K24" s="8">
+      <c r="K24" s="3">
         <v>59.109311740890689</v>
       </c>
-      <c r="L24" s="8">
+      <c r="L24" s="3">
         <v>0.43</v>
       </c>
-      <c r="M24" s="8">
-        <v>4</v>
-      </c>
-      <c r="N24" s="8">
+      <c r="M24" s="3">
+        <v>4</v>
+      </c>
+      <c r="N24" s="3">
         <v>2</v>
       </c>
-      <c r="O24" s="8">
+      <c r="O24" s="3">
         <v>5</v>
       </c>
-      <c r="P24" s="8">
+      <c r="P24" s="3">
         <v>5</v>
       </c>
-      <c r="Q24" s="8">
+      <c r="Q24" s="3">
         <v>52</v>
       </c>
-      <c r="R24" s="8">
+      <c r="R24" s="3">
         <v>20</v>
       </c>
-      <c r="S24" s="9" t="s">
+      <c r="S24" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="T24" s="8">
+      <c r="T24" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="U24" s="3">
         <v>-308.5</v>
       </c>
-      <c r="U24" s="8" t="s">
-        <v>229</v>
-      </c>
     </row>
-    <row r="25" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="8" t="s">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="C25" s="8">
+      <c r="C25" s="3">
         <v>783</v>
       </c>
-      <c r="D25" s="8">
+      <c r="D25" s="3">
         <v>75.47892720306514</v>
       </c>
-      <c r="E25" s="8" t="s">
+      <c r="E25" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="F25" s="8" t="s">
+      <c r="F25" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="G25" s="8" t="s">
+      <c r="G25" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="H25" s="8" t="s">
+      <c r="H25" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="I25" s="8">
+      <c r="I25" s="3">
         <v>0.33</v>
       </c>
-      <c r="J25" s="8">
+      <c r="J25" s="3">
         <v>-301.29998779296881</v>
       </c>
-      <c r="K25" s="8">
+      <c r="K25" s="3">
         <v>59.003831417624518</v>
       </c>
-      <c r="L25" s="8">
+      <c r="L25" s="3">
         <v>0.33</v>
       </c>
-      <c r="M25" s="8">
-        <v>4</v>
-      </c>
-      <c r="N25" s="8">
+      <c r="M25" s="3">
+        <v>4</v>
+      </c>
+      <c r="N25" s="3">
         <v>3</v>
       </c>
-      <c r="O25" s="8">
-        <v>4</v>
-      </c>
-      <c r="P25" s="8">
-        <v>4</v>
-      </c>
-      <c r="Q25" s="8">
+      <c r="O25" s="3">
+        <v>4</v>
+      </c>
+      <c r="P25" s="3">
+        <v>4</v>
+      </c>
+      <c r="Q25" s="3">
         <v>72</v>
       </c>
-      <c r="R25" s="8">
+      <c r="R25" s="3">
         <v>28</v>
       </c>
-      <c r="S25" s="9" t="s">
+      <c r="S25" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="T25" s="8">
+      <c r="T25" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="U25" s="3">
         <v>-435.20001220703119</v>
       </c>
-      <c r="U25" s="8" t="s">
-        <v>230</v>
-      </c>
     </row>
-    <row r="26" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="8" t="s">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C26" s="8">
+      <c r="C26" s="3">
         <v>393</v>
       </c>
-      <c r="D26" s="8">
+      <c r="D26" s="3">
         <v>71.755725190839698</v>
       </c>
-      <c r="E26" s="8" t="s">
+      <c r="E26" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="F26" s="8" t="s">
+      <c r="F26" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="G26" s="8" t="s">
+      <c r="G26" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="H26" s="8" t="s">
+      <c r="H26" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="I26" s="8">
+      <c r="I26" s="3">
         <v>0.39</v>
       </c>
-      <c r="J26" s="8">
+      <c r="J26" s="3">
         <v>-162.1000061035156</v>
       </c>
-      <c r="K26" s="8">
+      <c r="K26" s="3">
         <v>60.050890585241731</v>
       </c>
-      <c r="L26" s="8">
+      <c r="L26" s="3">
         <v>0.38</v>
       </c>
-      <c r="M26" s="8">
-        <v>4</v>
-      </c>
-      <c r="N26" s="8">
+      <c r="M26" s="3">
+        <v>4</v>
+      </c>
+      <c r="N26" s="3">
         <v>3</v>
       </c>
-      <c r="O26" s="8">
+      <c r="O26" s="3">
         <v>3</v>
       </c>
-      <c r="P26" s="8">
-        <v>4</v>
-      </c>
-      <c r="Q26" s="8">
+      <c r="P26" s="3">
+        <v>4</v>
+      </c>
+      <c r="Q26" s="3">
         <v>57</v>
       </c>
-      <c r="R26" s="8">
+      <c r="R26" s="3">
         <v>24</v>
       </c>
-      <c r="S26" s="9" t="s">
+      <c r="S26" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="T26" s="8">
+      <c r="T26" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="U26" s="3">
         <v>-193.19999694824219</v>
       </c>
-      <c r="U26" s="8" t="s">
-        <v>231</v>
-      </c>
     </row>
-    <row r="27" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="8" t="s">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="C27" s="8">
+      <c r="C27" s="3">
         <v>729</v>
       </c>
-      <c r="D27" s="8">
+      <c r="D27" s="3">
         <v>41.975308641975303</v>
       </c>
-      <c r="E27" s="8" t="s">
+      <c r="E27" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="F27" s="8" t="s">
+      <c r="F27" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="G27" s="8" t="s">
+      <c r="G27" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="H27" s="8" t="s">
+      <c r="H27" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="I27" s="8">
+      <c r="I27" s="3">
         <v>0.36</v>
       </c>
-      <c r="J27" s="8">
+      <c r="J27" s="3">
         <v>-242.69999694824219</v>
       </c>
-      <c r="K27" s="8">
+      <c r="K27" s="3">
         <v>58.573388203017828</v>
       </c>
-      <c r="L27" s="8">
+      <c r="L27" s="3">
         <v>0.46</v>
       </c>
-      <c r="M27" s="8">
+      <c r="M27" s="3">
         <v>3</v>
       </c>
-      <c r="N27" s="8">
+      <c r="N27" s="3">
         <v>6</v>
       </c>
-      <c r="O27" s="8">
+      <c r="O27" s="3">
         <v>5</v>
       </c>
-      <c r="P27" s="8">
+      <c r="P27" s="3">
         <v>3</v>
       </c>
-      <c r="Q27" s="8">
+      <c r="Q27" s="3">
         <v>66</v>
       </c>
-      <c r="R27" s="8">
+      <c r="R27" s="3">
         <v>25</v>
       </c>
-      <c r="S27" s="9" t="s">
+      <c r="S27" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="T27" s="8">
+      <c r="T27" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="U27" s="3">
         <v>-185.69999694824219</v>
       </c>
-      <c r="U27" s="8" t="s">
-        <v>232</v>
-      </c>
     </row>
-    <row r="28" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="8" t="s">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="C28" s="8">
+      <c r="C28" s="3">
         <v>330</v>
       </c>
-      <c r="D28" s="8">
+      <c r="D28" s="3">
         <v>40.606060606060609</v>
       </c>
-      <c r="E28" s="8" t="s">
+      <c r="E28" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="F28" s="8" t="s">
+      <c r="F28" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G28" s="8" t="s">
+      <c r="G28" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="H28" s="8" t="s">
+      <c r="H28" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="I28" s="8">
+      <c r="I28" s="3">
         <v>0.39</v>
       </c>
-      <c r="J28" s="8">
+      <c r="J28" s="3">
         <v>-124.5</v>
       </c>
-      <c r="K28" s="8">
+      <c r="K28" s="3">
         <v>59.393939393939398</v>
       </c>
-      <c r="L28" s="8">
+      <c r="L28" s="3">
         <v>0.48</v>
       </c>
-      <c r="M28" s="8">
-        <v>4</v>
-      </c>
-      <c r="N28" s="8">
+      <c r="M28" s="3">
+        <v>4</v>
+      </c>
+      <c r="N28" s="3">
         <v>2</v>
       </c>
-      <c r="O28" s="8">
+      <c r="O28" s="3">
         <v>3</v>
       </c>
-      <c r="P28" s="8">
+      <c r="P28" s="3">
         <v>2</v>
       </c>
-      <c r="Q28" s="8">
+      <c r="Q28" s="3">
         <v>60</v>
       </c>
-      <c r="R28" s="8">
+      <c r="R28" s="3">
         <v>23</v>
       </c>
-      <c r="S28" s="9" t="s">
+      <c r="S28" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="T28" s="8">
+      <c r="T28" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="U28" s="3">
         <v>-81.699996948242188</v>
       </c>
-      <c r="U28" s="8" t="s">
-        <v>233</v>
-      </c>
     </row>
-    <row r="29" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="8" t="s">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="C29" s="8">
+      <c r="C29" s="3">
         <v>282</v>
       </c>
-      <c r="D29" s="8">
+      <c r="D29" s="3">
         <v>39.00709219858156</v>
       </c>
-      <c r="E29" s="8" t="s">
+      <c r="E29" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="F29" s="8" t="s">
+      <c r="F29" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="G29" s="8" t="s">
+      <c r="G29" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="H29" s="8" t="s">
+      <c r="H29" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="I29" s="8">
+      <c r="I29" s="3">
         <v>0.38</v>
       </c>
-      <c r="J29" s="8">
+      <c r="J29" s="3">
         <v>-90.400001525878906</v>
       </c>
-      <c r="K29" s="8">
+      <c r="K29" s="3">
         <v>57.446808510638313</v>
       </c>
-      <c r="L29" s="8">
+      <c r="L29" s="3">
         <v>0.46</v>
       </c>
-      <c r="M29" s="8">
+      <c r="M29" s="3">
         <v>3</v>
       </c>
-      <c r="N29" s="8">
+      <c r="N29" s="3">
         <v>5</v>
       </c>
-      <c r="O29" s="8">
+      <c r="O29" s="3">
         <v>3</v>
       </c>
-      <c r="P29" s="8">
+      <c r="P29" s="3">
         <v>2</v>
       </c>
-      <c r="Q29" s="8">
+      <c r="Q29" s="3">
         <v>68</v>
       </c>
-      <c r="R29" s="8">
+      <c r="R29" s="3">
         <v>30</v>
       </c>
-      <c r="S29" s="9" t="s">
+      <c r="S29" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="T29" s="8">
+      <c r="T29" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="U29" s="3">
         <v>-52.700000762939453</v>
-      </c>
-      <c r="U29" s="8" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.3">
@@ -3061,7 +3048,7 @@
       <c r="E30" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="F30" s="7" t="s">
+      <c r="F30" s="3" t="s">
         <v>167</v>
       </c>
       <c r="G30" s="3" t="s">
@@ -3103,11 +3090,11 @@
       <c r="S30" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="T30" s="3">
+      <c r="T30" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="U30" s="3">
         <v>-93.400001525878906</v>
-      </c>
-      <c r="U30" s="3" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.3">
@@ -3126,7 +3113,7 @@
       <c r="E31" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="F31" s="7" t="s">
+      <c r="F31" s="3" t="s">
         <v>172</v>
       </c>
       <c r="G31" s="3" t="s">
@@ -3168,11 +3155,11 @@
       <c r="S31" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="T31" s="3">
+      <c r="T31" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="U31" s="3">
         <v>-168.16999816894531</v>
-      </c>
-      <c r="U31" s="3" t="s">
-        <v>236</v>
       </c>
     </row>
   </sheetData>
